--- a/data/point_data/N3_142_UMi.xlsx
+++ b/data/point_data/N3_142_UMi.xlsx
@@ -880,25 +880,25 @@
         <v>103.301546771324</v>
       </c>
       <c r="G4" s="22" t="n">
-        <v>103.365815193022</v>
+        <v>103.49</v>
       </c>
       <c r="H4" s="24" t="n">
-        <v>102.638833315253</v>
+        <v>102.64</v>
       </c>
       <c r="I4" s="23" t="n">
         <v>5.67954731696836</v>
       </c>
       <c r="J4" s="22" t="n">
-        <v>0.853436216586171</v>
+        <v>7.67</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>13.9882115793548</v>
+        <v>7.49</v>
       </c>
       <c r="L4" s="23" t="n">
         <v>9.26</v>
       </c>
       <c r="M4" s="22" t="n">
-        <v>3.26</v>
+        <v>9.26</v>
       </c>
       <c r="N4" s="24" t="n">
         <v>3.26</v>
@@ -907,7 +907,7 @@
         <v>8.25</v>
       </c>
       <c r="P4" s="22" t="n">
-        <v>3.26</v>
+        <v>8.25</v>
       </c>
       <c r="Q4" s="24" t="n">
         <v>3.26</v>
@@ -933,25 +933,25 @@
         <v>102.678768862451</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>102.618440808765</v>
+        <v>103.11</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>102.141585146539</v>
+        <v>102.14</v>
       </c>
       <c r="I5" s="23" t="n">
         <v>0.8871056916269771</v>
       </c>
       <c r="J5" s="22" t="n">
-        <v>0.903040618642867</v>
+        <v>2.89</v>
       </c>
       <c r="K5" s="24" t="n">
-        <v>0.864858213763812</v>
+        <v>3.19</v>
       </c>
       <c r="L5" s="23" t="n">
         <v>10.26</v>
       </c>
       <c r="M5" s="22" t="n">
-        <v>3.26</v>
+        <v>10.26</v>
       </c>
       <c r="N5" s="24" t="n">
         <v>3.26</v>
@@ -960,7 +960,7 @@
         <v>1.96</v>
       </c>
       <c r="P5" s="22" t="n">
-        <v>3.26</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" s="24" t="n">
         <v>3.26</v>
@@ -986,25 +986,25 @@
         <v>112.207496639433</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>127.623745575164</v>
+        <v>127.47</v>
       </c>
       <c r="H6" s="24" t="n">
-        <v>126.495989292562</v>
+        <v>126.45</v>
       </c>
       <c r="I6" s="23" t="n">
         <v>84.3678817362303</v>
       </c>
       <c r="J6" s="22" t="n">
-        <v>12.5672537280377</v>
+        <v>19.51</v>
       </c>
       <c r="K6" s="24" t="n">
-        <v>16.6190032678546</v>
+        <v>19.78</v>
       </c>
       <c r="L6" s="23" t="n">
         <v>67.02</v>
       </c>
       <c r="M6" s="22" t="n">
-        <v>70.84999999999999</v>
+        <v>67.02</v>
       </c>
       <c r="N6" s="24" t="n">
         <v>70.84999999999999</v>
@@ -1013,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="22" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="24" t="n">
         <v>3.26</v>
@@ -1039,25 +1039,25 @@
         <v>104.843796353737</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>131.007138172925</v>
+        <v>131.51</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>129.808204363597</v>
+        <v>129.69</v>
       </c>
       <c r="I7" s="23" t="n">
         <v>75.5947599180942</v>
       </c>
       <c r="J7" s="22" t="n">
-        <v>12.2557627939194</v>
+        <v>12.26</v>
       </c>
       <c r="K7" s="24" t="n">
-        <v>13.0403813958827</v>
+        <v>13.07</v>
       </c>
       <c r="L7" s="23" t="n">
         <v>51.76</v>
       </c>
       <c r="M7" s="22" t="n">
-        <v>54.87</v>
+        <v>51.76</v>
       </c>
       <c r="N7" s="24" t="n">
         <v>54.87</v>
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="22" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="24" t="n">
         <v>3.26</v>
@@ -1092,25 +1092,25 @@
         <v>105.733479238877</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>127.544532715833</v>
+        <v>128.19</v>
       </c>
       <c r="H8" s="24" t="n">
-        <v>126.950128700832</v>
+        <v>126.93</v>
       </c>
       <c r="I8" s="23" t="n">
         <v>70.48278293113999</v>
       </c>
       <c r="J8" s="22" t="n">
-        <v>24.0372910333872</v>
+        <v>25.04</v>
       </c>
       <c r="K8" s="24" t="n">
-        <v>23.2806692929644</v>
+        <v>23.13</v>
       </c>
       <c r="L8" s="23" t="n">
         <v>42.71</v>
       </c>
       <c r="M8" s="22" t="n">
-        <v>50.27</v>
+        <v>42.71</v>
       </c>
       <c r="N8" s="24" t="n">
         <v>50.27</v>
@@ -1119,7 +1119,7 @@
         <v>1.81</v>
       </c>
       <c r="P8" s="22" t="n">
-        <v>3.26</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" s="24" t="n">
         <v>3.26</v>
@@ -1145,25 +1145,25 @@
         <v>112.855916025352</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>138.612889953472</v>
+        <v>138.43</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>137.069436389916</v>
+        <v>136.94</v>
       </c>
       <c r="I9" s="23" t="n">
         <v>149.668779471205</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>53.0581117418056</v>
+        <v>53.06</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>56.4838705401877</v>
+        <v>56.47</v>
       </c>
       <c r="L9" s="23" t="n">
         <v>41.29</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>41.8</v>
+        <v>41.29</v>
       </c>
       <c r="N9" s="24" t="n">
         <v>41.8</v>
@@ -1172,7 +1172,7 @@
         <v>8.08</v>
       </c>
       <c r="P9" s="22" t="n">
-        <v>9.1</v>
+        <v>8.08</v>
       </c>
       <c r="Q9" s="24" t="n">
         <v>9.1</v>
@@ -1198,25 +1198,25 @@
         <v>110.080483375175</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>112.347718144089</v>
+        <v>112.67</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>110.835800783751</v>
+        <v>110.83</v>
       </c>
       <c r="I10" s="23" t="n">
         <v>96.177362048227</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>22.4578604286789</v>
+        <v>23.17</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>20.8743548778678</v>
+        <v>22.04</v>
       </c>
       <c r="L10" s="23" t="n">
         <v>48.82</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>52.03</v>
+        <v>48.82</v>
       </c>
       <c r="N10" s="24" t="n">
         <v>52.03</v>
@@ -1225,7 +1225,7 @@
         <v>5.2</v>
       </c>
       <c r="P10" s="22" t="n">
-        <v>5.41</v>
+        <v>5.2</v>
       </c>
       <c r="Q10" s="24" t="n">
         <v>5.41</v>
@@ -1251,25 +1251,25 @@
         <v>106.519720168088</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>104.86938541782</v>
+        <v>106.16</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>104.407280372534</v>
+        <v>104.41</v>
       </c>
       <c r="I11" s="23" t="n">
         <v>6.73330240590593</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.7443712896503279</v>
+        <v>6.16</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.801942844157287</v>
+        <v>5.52</v>
       </c>
       <c r="L11" s="23" t="n">
         <v>5.23</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>3.26</v>
+        <v>5.23</v>
       </c>
       <c r="N11" s="24" t="n">
         <v>3.26</v>
@@ -1278,7 +1278,7 @@
         <v>0.61</v>
       </c>
       <c r="P11" s="22" t="n">
-        <v>3.26</v>
+        <v>0.61</v>
       </c>
       <c r="Q11" s="24" t="n">
         <v>3.26</v>
@@ -1304,25 +1304,25 @@
         <v>118.48901605282</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>105.780356327024</v>
+        <v>106.36</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>105.059205772312</v>
+        <v>105.05</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>92.75876818784241</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>6.22641907869362</v>
+        <v>17.3</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>12.3967437889213</v>
+        <v>16.46</v>
       </c>
       <c r="L12" s="23" t="n">
         <v>9.140000000000001</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>3.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N12" s="24" t="n">
         <v>3.26</v>
@@ -1331,7 +1331,7 @@
         <v>3.94</v>
       </c>
       <c r="P12" s="22" t="n">
-        <v>3.26</v>
+        <v>3.94</v>
       </c>
       <c r="Q12" s="24" t="n">
         <v>3.26</v>
@@ -1361,25 +1361,25 @@
         <v>115.975816966833</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>113.00213492235</v>
+        <v>113.57</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>112.048285407485</v>
+        <v>112.05</v>
       </c>
       <c r="I13" s="23" t="n">
         <v>60.6397542302689</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>131.119634702618</v>
+        <v>28.1</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>6.9997821443576</v>
+        <v>31.96</v>
       </c>
       <c r="L13" s="23" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" s="22" t="n">
-        <v>3.26</v>
+        <v>11.11</v>
       </c>
       <c r="N13" s="24" t="n">
         <v>3.26</v>
@@ -1388,7 +1388,7 @@
         <v>7.65</v>
       </c>
       <c r="P13" s="22" t="n">
-        <v>3.26</v>
+        <v>7.65</v>
       </c>
       <c r="Q13" s="24" t="n">
         <v>3.26</v>
@@ -1447,25 +1447,25 @@
         <v>121.396848924396</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>110.515136921376</v>
+        <v>110.76</v>
       </c>
       <c r="H15" s="24" t="n">
-        <v>109.245860407103</v>
+        <v>109.24</v>
       </c>
       <c r="I15" s="23" t="n">
         <v>13.3732925126948</v>
       </c>
       <c r="J15" s="22" t="n">
-        <v>5.32297543306555</v>
+        <v>30.08</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>5.37075671539116</v>
+        <v>26.99</v>
       </c>
       <c r="L15" s="23" t="n">
         <v>23.72</v>
       </c>
       <c r="M15" s="22" t="n">
-        <v>3.26</v>
+        <v>23.72</v>
       </c>
       <c r="N15" s="24" t="n">
         <v>3.26</v>
@@ -1474,7 +1474,7 @@
         <v>6.5</v>
       </c>
       <c r="P15" s="22" t="n">
-        <v>3.26</v>
+        <v>6.5</v>
       </c>
       <c r="Q15" s="24" t="n">
         <v>3.26</v>
@@ -1500,25 +1500,25 @@
         <v>116.213415566529</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>106.618621278387</v>
+        <v>106.75</v>
       </c>
       <c r="H16" s="24" t="n">
-        <v>105.665050443648</v>
+        <v>105.66</v>
       </c>
       <c r="I16" s="23" t="n">
         <v>54.1420341799513</v>
       </c>
       <c r="J16" s="22" t="n">
-        <v>5.95580080131159</v>
+        <v>18.48</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>11.9597345851095</v>
+        <v>17.64</v>
       </c>
       <c r="L16" s="23" t="n">
         <v>11.81</v>
       </c>
       <c r="M16" s="22" t="n">
-        <v>3.26</v>
+        <v>11.81</v>
       </c>
       <c r="N16" s="24" t="n">
         <v>3.26</v>
@@ -1527,7 +1527,7 @@
         <v>4.04</v>
       </c>
       <c r="P16" s="22" t="n">
-        <v>3.26</v>
+        <v>4.04</v>
       </c>
       <c r="Q16" s="24" t="n">
         <v>3.26</v>
@@ -1557,25 +1557,25 @@
         <v>108.308215582765</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>133.400970553384</v>
+        <v>133.4</v>
       </c>
       <c r="H17" s="24" t="n">
-        <v>130.637160583058</v>
+        <v>130.64</v>
       </c>
       <c r="I17" s="23" t="n">
         <v>7.07395989144194</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>15.9686642950186</v>
+        <v>15.97</v>
       </c>
       <c r="K17" s="24" t="n">
-        <v>16.2289137718248</v>
+        <v>16.06</v>
       </c>
       <c r="L17" s="23" t="n">
         <v>11.8</v>
       </c>
       <c r="M17" s="22" t="n">
-        <v>10.89</v>
+        <v>11.8</v>
       </c>
       <c r="N17" s="24" t="n">
         <v>10.89</v>
@@ -1584,7 +1584,7 @@
         <v>5.49</v>
       </c>
       <c r="P17" s="22" t="n">
-        <v>6.68</v>
+        <v>5.49</v>
       </c>
       <c r="Q17" s="24" t="n">
         <v>6.68</v>
@@ -1610,25 +1610,25 @@
         <v>108.397823537568</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>118.507044544662</v>
+        <v>118.8</v>
       </c>
       <c r="H18" s="24" t="n">
-        <v>116.783518327827</v>
+        <v>116.78</v>
       </c>
       <c r="I18" s="23" t="n">
         <v>90.36973773362971</v>
       </c>
       <c r="J18" s="22" t="n">
-        <v>29.4509672570088</v>
+        <v>26.33</v>
       </c>
       <c r="K18" s="24" t="n">
-        <v>26.1810044232462</v>
+        <v>27.11</v>
       </c>
       <c r="L18" s="23" t="n">
         <v>12.3</v>
       </c>
       <c r="M18" s="22" t="n">
-        <v>13.48</v>
+        <v>12.3</v>
       </c>
       <c r="N18" s="24" t="n">
         <v>13.48</v>
@@ -1637,7 +1637,7 @@
         <v>21.56</v>
       </c>
       <c r="P18" s="22" t="n">
-        <v>25.11</v>
+        <v>21.56</v>
       </c>
       <c r="Q18" s="24" t="n">
         <v>25.11</v>
@@ -1663,25 +1663,25 @@
         <v>111.941248968871</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>116.015459544844</v>
+        <v>117.03</v>
       </c>
       <c r="H19" s="24" t="n">
-        <v>114.669616204173</v>
+        <v>115.13</v>
       </c>
       <c r="I19" s="23" t="n">
         <v>45.2988656569671</v>
       </c>
       <c r="J19" s="22" t="n">
-        <v>0.728224861967817</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.728687548184148</v>
+        <v>8.25</v>
       </c>
       <c r="L19" s="23" t="n">
         <v>6.53</v>
       </c>
       <c r="M19" s="22" t="n">
-        <v>3.26</v>
+        <v>6.53</v>
       </c>
       <c r="N19" s="24" t="n">
         <v>3.26</v>
@@ -1690,7 +1690,7 @@
         <v>2.7</v>
       </c>
       <c r="P19" s="22" t="n">
-        <v>3.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q19" s="24" t="n">
         <v>3.26</v>
@@ -1716,25 +1716,25 @@
         <v>107.343998739454</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>121.469078494858</v>
+        <v>122.76</v>
       </c>
       <c r="H20" s="24" t="n">
-        <v>120.619298684967</v>
+        <v>120.61</v>
       </c>
       <c r="I20" s="23" t="n">
         <v>0.858385967884338</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>0.950467900646607</v>
+        <v>14.95</v>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.877247054876527</v>
+        <v>11.7</v>
       </c>
       <c r="L20" s="23" t="n">
         <v>10.21</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>3.96</v>
+        <v>10.21</v>
       </c>
       <c r="N20" s="24" t="n">
         <v>3.96</v>
@@ -1743,7 +1743,7 @@
         <v>1.86</v>
       </c>
       <c r="P20" s="22" t="n">
-        <v>3.26</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" s="24" t="n">
         <v>3.26</v>
@@ -1773,25 +1773,25 @@
         <v>127.214197875135</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>130.93259555311</v>
+        <v>129.54</v>
       </c>
       <c r="H21" s="24" t="n">
-        <v>129.968557929382</v>
+        <v>128.21</v>
       </c>
       <c r="I21" s="23" t="n">
         <v>19.5003234083295</v>
       </c>
       <c r="J21" s="22" t="n">
-        <v>0.707922050616729</v>
+        <v>30.65</v>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.695070472981382</v>
+        <v>26.38</v>
       </c>
       <c r="L21" s="23" t="n">
         <v>18.88</v>
       </c>
       <c r="M21" s="22" t="n">
-        <v>3.26</v>
+        <v>18.88</v>
       </c>
       <c r="N21" s="24" t="n">
         <v>3.26</v>
@@ -1800,7 +1800,7 @@
         <v>2.92</v>
       </c>
       <c r="P21" s="22" t="n">
-        <v>4.42</v>
+        <v>2.92</v>
       </c>
       <c r="Q21" s="24" t="n">
         <v>4.42</v>
@@ -1826,25 +1826,25 @@
         <v>130.895331545699</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>116.249784447813</v>
+        <v>115.78</v>
       </c>
       <c r="H22" s="24" t="n">
-        <v>115.032287870517</v>
+        <v>113.31</v>
       </c>
       <c r="I22" s="23" t="n">
         <v>12.2704390014645</v>
       </c>
       <c r="J22" s="22" t="n">
-        <v>1.02282414560122</v>
+        <v>22.78</v>
       </c>
       <c r="K22" s="24" t="n">
-        <v>1.01937206419663</v>
+        <v>17.17</v>
       </c>
       <c r="L22" s="23" t="n">
         <v>7.9</v>
       </c>
       <c r="M22" s="22" t="n">
-        <v>4.99</v>
+        <v>7.9</v>
       </c>
       <c r="N22" s="24" t="n">
         <v>4.99</v>
@@ -1853,7 +1853,7 @@
         <v>2.4</v>
       </c>
       <c r="P22" s="22" t="n">
-        <v>3.26</v>
+        <v>2.4</v>
       </c>
       <c r="Q22" s="24" t="n">
         <v>3.26</v>
@@ -1879,25 +1879,25 @@
         <v>127.450238295316</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>108.351404903408</v>
+        <v>106.78</v>
       </c>
       <c r="H23" s="24" t="n">
-        <v>106.820101315278</v>
+        <v>105.1</v>
       </c>
       <c r="I23" s="23" t="n">
         <v>24.2509272823452</v>
       </c>
       <c r="J23" s="22" t="n">
-        <v>6.31209312954043</v>
+        <v>7.59</v>
       </c>
       <c r="K23" s="24" t="n">
-        <v>9.71525067762891</v>
+        <v>7.7</v>
       </c>
       <c r="L23" s="23" t="n">
         <v>10.08</v>
       </c>
       <c r="M23" s="22" t="n">
-        <v>7.14</v>
+        <v>10.08</v>
       </c>
       <c r="N23" s="24" t="n">
         <v>7.14</v>
@@ -1906,7 +1906,7 @@
         <v>12.91</v>
       </c>
       <c r="P23" s="22" t="n">
-        <v>13.42</v>
+        <v>12.91</v>
       </c>
       <c r="Q23" s="24" t="n">
         <v>13.42</v>
@@ -1932,25 +1932,25 @@
         <v>138.454783036468</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>141.117291102672</v>
+        <v>139.4</v>
       </c>
       <c r="H24" s="24" t="n">
-        <v>139.91537497352</v>
+        <v>138.24</v>
       </c>
       <c r="I24" s="23" t="n">
         <v>53.1855001935885</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>0.582030502847241</v>
+        <v>0.58</v>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.550756012825778</v>
+        <v>0.54</v>
       </c>
       <c r="L24" s="23" t="n">
         <v>3.39</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>4.96</v>
+        <v>3.39</v>
       </c>
       <c r="N24" s="24" t="n">
         <v>4.96</v>
@@ -1959,7 +1959,7 @@
         <v>3.39</v>
       </c>
       <c r="P24" s="22" t="n">
-        <v>4.96</v>
+        <v>3.39</v>
       </c>
       <c r="Q24" s="24" t="n">
         <v>4.96</v>
@@ -1989,25 +1989,25 @@
         <v>133.362970258893</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>117.056783903922</v>
+        <v>116.95</v>
       </c>
       <c r="H25" s="24" t="n">
-        <v>115.429611456873</v>
+        <v>115.39</v>
       </c>
       <c r="I25" s="23" t="n">
         <v>15.9993892834998</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>39.8127976155606</v>
+        <v>45.88</v>
       </c>
       <c r="K25" s="24" t="n">
-        <v>38.2136599640269</v>
+        <v>41.82</v>
       </c>
       <c r="L25" s="23" t="n">
         <v>49.65</v>
       </c>
       <c r="M25" s="22" t="n">
-        <v>57.48</v>
+        <v>49.65</v>
       </c>
       <c r="N25" s="24" t="n">
         <v>57.48</v>
@@ -2016,7 +2016,7 @@
         <v>10.41</v>
       </c>
       <c r="P25" s="22" t="n">
-        <v>10.09</v>
+        <v>10.41</v>
       </c>
       <c r="Q25" s="24" t="n">
         <v>10.09</v>
@@ -2042,25 +2042,25 @@
         <v>130.722990115359</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>108.447541242252</v>
+        <v>108.98</v>
       </c>
       <c r="H26" s="24" t="n">
-        <v>107.198401200598</v>
+        <v>107.2</v>
       </c>
       <c r="I26" s="23" t="n">
         <v>30.6848956168062</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>6.97144058887532</v>
+        <v>17.88</v>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.809230033096765</v>
+        <v>15.55</v>
       </c>
       <c r="L26" s="23" t="n">
         <v>10.16</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>3.26</v>
+        <v>10.16</v>
       </c>
       <c r="N26" s="24" t="n">
         <v>3.26</v>
@@ -2069,7 +2069,7 @@
         <v>7.97</v>
       </c>
       <c r="P26" s="22" t="n">
-        <v>3.26</v>
+        <v>7.97</v>
       </c>
       <c r="Q26" s="24" t="n">
         <v>3.26</v>
@@ -2095,25 +2095,25 @@
         <v>140.83199798751</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>127.217515921121</v>
+        <v>126.11</v>
       </c>
       <c r="H27" s="24" t="n">
-        <v>122.648049276166</v>
+        <v>122.63</v>
       </c>
       <c r="I27" s="23" t="n">
         <v>0.638332653215</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>0.824792831355912</v>
+        <v>47.02</v>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.792020227718451</v>
+        <v>36.54</v>
       </c>
       <c r="L27" s="23" t="n">
         <v>33.1</v>
       </c>
       <c r="M27" s="22" t="n">
-        <v>5.18</v>
+        <v>33.1</v>
       </c>
       <c r="N27" s="24" t="n">
         <v>5.18</v>
@@ -2122,7 +2122,7 @@
         <v>17.65</v>
       </c>
       <c r="P27" s="22" t="n">
-        <v>19.43</v>
+        <v>17.65</v>
       </c>
       <c r="Q27" s="24" t="n">
         <v>19.43</v>
@@ -2148,25 +2148,25 @@
         <v>116.754572019895</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>111.936552254142</v>
+        <v>112.29</v>
       </c>
       <c r="H28" s="24" t="n">
-        <v>109.657665001166</v>
+        <v>110.93</v>
       </c>
       <c r="I28" s="23" t="n">
         <v>57.7091726103711</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>0.770577022122943</v>
+        <v>1.34</v>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.886846027117775</v>
+        <v>1.39</v>
       </c>
       <c r="L28" s="23" t="n">
         <v>3.29</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="N28" s="24" t="n">
         <v>3.26</v>
@@ -2175,7 +2175,7 @@
         <v>2.83</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>3.26</v>
+        <v>2.83</v>
       </c>
       <c r="Q28" s="24" t="n">
         <v>3.26</v>
@@ -2205,25 +2205,25 @@
         <v>125.879402435007</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>107.331725004988</v>
+        <v>106.48</v>
       </c>
       <c r="H29" s="24" t="n">
-        <v>105.584988260575</v>
+        <v>104.03</v>
       </c>
       <c r="I29" s="23" t="n">
         <v>45.6604492280968</v>
       </c>
       <c r="J29" s="22" t="n">
-        <v>12.530336790432</v>
+        <v>17.74</v>
       </c>
       <c r="K29" s="24" t="n">
-        <v>105.319268489712</v>
+        <v>18.66</v>
       </c>
       <c r="L29" s="23" t="n">
         <v>6.83</v>
       </c>
       <c r="M29" s="22" t="n">
-        <v>4.68</v>
+        <v>6.83</v>
       </c>
       <c r="N29" s="24" t="n">
         <v>4.68</v>
@@ -2232,7 +2232,7 @@
         <v>4.41</v>
       </c>
       <c r="P29" s="22" t="n">
-        <v>4.85</v>
+        <v>4.41</v>
       </c>
       <c r="Q29" s="24" t="n">
         <v>4.85</v>
@@ -2258,25 +2258,25 @@
         <v>117.08507760364</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>117.179897221904</v>
+        <v>115.54</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>114.744850126146</v>
+        <v>113.19</v>
       </c>
       <c r="I30" s="23" t="n">
         <v>49.5654842589371</v>
       </c>
       <c r="J30" s="22" t="n">
-        <v>22.8699118746382</v>
+        <v>23.84</v>
       </c>
       <c r="K30" s="24" t="n">
-        <v>22.5915077630794</v>
+        <v>23.57</v>
       </c>
       <c r="L30" s="23" t="n">
         <v>62.7</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>61.45</v>
+        <v>62.7</v>
       </c>
       <c r="N30" s="24" t="n">
         <v>61.45</v>
@@ -2285,7 +2285,7 @@
         <v>31.12</v>
       </c>
       <c r="P30" s="22" t="n">
-        <v>31.83</v>
+        <v>31.12</v>
       </c>
       <c r="Q30" s="24" t="n">
         <v>31.83</v>
@@ -2311,25 +2311,25 @@
         <v>123.702897617723</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>123.936734936614</v>
+        <v>122.78</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>121.685216679221</v>
+        <v>120.12</v>
       </c>
       <c r="I31" s="23" t="n">
         <v>34.0787777926185</v>
       </c>
       <c r="J31" s="22" t="n">
-        <v>16.1907832296544</v>
+        <v>35.99</v>
       </c>
       <c r="K31" s="24" t="n">
-        <v>13.6603744679624</v>
+        <v>29.76</v>
       </c>
       <c r="L31" s="23" t="n">
         <v>29.66</v>
       </c>
       <c r="M31" s="22" t="n">
-        <v>34.88</v>
+        <v>29.66</v>
       </c>
       <c r="N31" s="24" t="n">
         <v>34.88</v>
@@ -2338,7 +2338,7 @@
         <v>22.12</v>
       </c>
       <c r="P31" s="22" t="n">
-        <v>3.97</v>
+        <v>22.12</v>
       </c>
       <c r="Q31" s="24" t="n">
         <v>3.97</v>
